--- a/scripts/prologue.xlsx
+++ b/scripts/prologue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB98B498-C008-47F9-9FD8-CCA5CFB5F310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB467B7-FE1B-4591-A49A-90DDD678B0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="379">
   <si>
     <t>speaker</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,10 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>??</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -58,10 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>align</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>choice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -491,10 +483,6 @@
     <t>choice</t>
   </si>
   <si>
-    <t>국장'의 결장이야</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그럼 자네가 날 이끌어줘</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -706,10 +694,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>국장', 당신... 족쇄는 찾았습니까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그림자는 당신의 목을 움켜쥔 채 뼛속까지 저며오는 살의를 드러내고 있었다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1472,6 +1456,14 @@
   </si>
   <si>
     <t>...○○, 나 기억해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'국장', 당신... 족쇄는 찾았습니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'국장'의 결장이야</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1879,18 +1871,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEC9E4D-1BC2-47C1-B354-5864E5DC6C7E}">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.83203125" style="4" customWidth="1"/>
-    <col min="4" max="8" width="9" style="2"/>
+    <col min="4" max="6" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1899,195 +1891,192 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C5" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C16" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C21" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B22" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B23" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="C23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C27" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C27" s="4" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
@@ -2100,18 +2089,18 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -2119,368 +2108,360 @@
         <v>28</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C34" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C35" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4" t="s">
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C38" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="4" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C40" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C39" s="4" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B41" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C41" s="4" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="4" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C46" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B45" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B47" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="C47" s="4" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B49" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="C49" s="4" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C50" s="4" t="s">
+      <c r="A50" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C51" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B52" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C52" s="4" t="s">
+    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C53" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="4" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C55" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C54" s="4" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B56" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C56" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
-        <v>8</v>
+      <c r="B58" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>206</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="4" t="s">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B62" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B65" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C66" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B68" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B65" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B66" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C67" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A68" s="2" t="s">
-        <v>250</v>
+      <c r="C68" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B69" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B71" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>209</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B72" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C73" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C74" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B73" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C74" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B75" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="C75" s="4" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B77" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C78" s="4" t="s">
+    </row>
+    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B79" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B79" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="4" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B80" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B80" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B81" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B82" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A82" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="A84" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2492,18 +2473,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7115359D-7475-477E-8932-F919DE4EA60B}">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="9" style="2"/>
+    <col min="4" max="6" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2512,977 +2493,971 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C4" s="6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C9" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="6" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C9" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="6" t="s">
+    <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="6" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="6" t="s">
+    <row r="15" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C14" s="6" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C18" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C22" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C27" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C28" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C30" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>120</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C44" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C48" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C52" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C54" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C56" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B62" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B63" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B64" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B65" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C66" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C67" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B68" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C71" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C72" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B73" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B75" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C77" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B78" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C80" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C81" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B82" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C83" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B84" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C85" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B88" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B89" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C90" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B96" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B97" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C98" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C99" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B100" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C101" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C103" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B105" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B107" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B108" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B109" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B110" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>176</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C111" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B114" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C115" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C117" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B118" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B119" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B120" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B121" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C123" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C124" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B125" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C126" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C127" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C128" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C130" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B131" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B132" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C133" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B134" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C135" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C136" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B137" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B139" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3494,18 +3469,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB64E87-5691-4BF1-B88C-0D9BCA723708}">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="4" max="6" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3514,441 +3489,435 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C3" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C4" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C9" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C10" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C14" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C4" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C9" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C10" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="6" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C14" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C28" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C36" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C46" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B49" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C52" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C55" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B56" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C57" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.45">
@@ -3963,18 +3932,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EB44A9-9BB2-4DDC-B33A-B25D27D1D6DE}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="4" max="6" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3983,511 +3952,505 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C6" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="6" t="s">
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C7" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C6" s="6" t="s">
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C7" s="6" t="s">
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="6" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="6" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="6" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="6" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B15" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="6" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>319</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C13" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C22" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C28" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C29" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C32" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C34" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B39" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C41" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C44" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C45" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C47" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B48" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B49" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C50" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B51" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C52" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.45">
       <c r="B53" s="3"/>
       <c r="C53" s="7" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C54" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/prologue.xlsx
+++ b/scripts/prologue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\p2n\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB467B7-FE1B-4591-A49A-90DDD678B0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AB36DB-1CBC-4963-A09D-28D939560553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="29475" yWindow="525" windowWidth="14250" windowHeight="15255" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -416,10 +416,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경청하며... 바다의 몽경에서 부는 바람을...</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>찾아서... 별과 불꽃을 흔드는 자를...</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1464,6 +1460,10 @@
   </si>
   <si>
     <t>'국장'의 결장이야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;blue&gt;경청하며... 바다의 몽경에서 부는 바람을...&lt;/blue&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1575,9 +1575,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1615,7 +1615,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1721,7 +1721,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1863,7 +1863,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1872,15 +1872,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEC9E4D-1BC2-47C1-B354-5864E5DC6C7E}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="4" customWidth="1"/>
     <col min="4" max="6" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1900,79 +1900,79 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C5" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1980,25 +1980,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C15" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,12 +2014,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
@@ -2027,12 +2027,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>14</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>3</v>
       </c>
@@ -2056,22 +2056,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C27" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>26</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>26</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>26</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>28</v>
       </c>
@@ -2111,12 +2111,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C34" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>26</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>26</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
@@ -2140,30 +2140,30 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C38" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C40" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>39</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -2179,57 +2179,57 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C46" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C51" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>39</v>
       </c>
@@ -2237,22 +2237,22 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C53" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C55" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>48</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
@@ -2268,23 +2268,23 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>51</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
@@ -2308,41 +2308,41 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B65" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B65" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C66" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>56</v>
       </c>
@@ -2350,23 +2350,23 @@
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>51</v>
       </c>
@@ -2374,25 +2374,25 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C73" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>56</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>61</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
         <v>61</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>51</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
         <v>61</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
         <v>61</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B81" s="3" t="s">
         <v>67</v>
       </c>
@@ -2448,20 +2448,20 @@
         <v>66</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2474,15 +2474,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7115359D-7475-477E-8932-F919DE4EA60B}">
   <dimension ref="A1:F141"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
     <col min="4" max="6" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -2502,12 +2502,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>68</v>
       </c>
@@ -2515,12 +2515,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>51</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
@@ -2536,15 +2536,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>72</v>
       </c>
@@ -2552,17 +2552,17 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="C9" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>51</v>
       </c>
@@ -2586,12 +2586,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C14" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>51</v>
       </c>
@@ -2615,17 +2615,17 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C18" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
@@ -2633,17 +2633,17 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C22" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
@@ -2675,17 +2675,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C27" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C28" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>51</v>
       </c>
@@ -2693,17 +2693,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C30" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C31" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
@@ -2711,12 +2711,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>61</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>61</v>
       </c>
@@ -2732,732 +2732,732 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C37" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="6" t="s">
+    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="6" t="s">
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C44" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C44" s="6" t="s">
+    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="6" t="s">
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="6" t="s">
+    <row r="47" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="6" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C48" s="8" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C49" s="6" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="6" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B51" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="6" t="s">
+    <row r="52" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C52" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C52" s="6" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C54" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="2" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C54" s="6" t="s">
+    <row r="56" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C56" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C56" s="6" t="s">
+    <row r="57" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B57" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="6" t="s">
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B62" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="s">
+      <c r="C62" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B63" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B64" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B65" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C67" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B68" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B62" s="3" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B70" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B63" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B64" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B65" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C66" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C67" s="6" t="s">
+      <c r="C70" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C71" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C72" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B73" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B68" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A69" s="2" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B74" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B75" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B76" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B78" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B70" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C71" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C72" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B73" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C73" s="6" t="s">
+    <row r="80" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C80" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C83" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B84" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B74" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B75" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B76" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C77" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B78" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C80" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C81" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B82" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C83" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B84" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C85" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B88" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B89" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A87" s="2" t="s">
+      <c r="C89" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B96" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B97" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C98" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C99" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B100" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C101" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B88" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B89" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C90" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A91" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A92" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A93" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A94" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A95" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B96" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B97" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C98" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C99" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B100" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C101" s="6" t="s">
+    <row r="103" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C103" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A102" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C103" s="6" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A104" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C104" s="6" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B105" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B105" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C107" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B108" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B108" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C108" s="6" t="s">
+    <row r="109" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B109" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B109" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C109" s="6" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B110" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C111" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B114" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C115" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C117" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B118" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B110" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C111" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A112" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A113" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B114" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C115" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A116" s="2" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B119" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B120" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B121" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C123" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C124" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B125" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C126" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C127" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C128" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C117" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B118" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B119" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B120" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B121" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C121" s="6" t="s">
+    <row r="130" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C130" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B131" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B132" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C133" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B134" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A122" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C122" s="6" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C135" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C136" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B137" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B139" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C123" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C124" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B125" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C126" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C127" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C128" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A129" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C130" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B131" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B132" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C133" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B134" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C135" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C136" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B137" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A138" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B139" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C139" s="6" t="s">
+      <c r="C140" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A140" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C140" s="6" t="s">
+    <row r="141" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="A141" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3470,15 +3470,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB64E87-5691-4BF1-B88C-0D9BCA723708}">
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="6" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="6" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -3498,429 +3498,429 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C4" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
+      <c r="C6" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="6" t="s">
+    <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="C9" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+    <row r="10" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C9" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C10" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="C12" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="6" t="s">
+    <row r="14" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="C14" s="6" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C14" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B18" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="6" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B19" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C19" s="6" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C20" s="6" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C21" s="6" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="6" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="6" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C31" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B26" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B27" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C28" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C31" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="6" t="s">
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C36" s="6" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C36" s="6" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="6" t="s">
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="6" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="6" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="A41" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C43" s="6" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="6" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C46" s="6" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C46" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="6" t="s">
+    <row r="50" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B50" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C52" s="6" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B53" s="3" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C55" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="2" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C55" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B56" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C57" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="6" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B60" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" s="6" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C118" s="7"/>
     </row>
   </sheetData>
@@ -3933,15 +3933,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EB44A9-9BB2-4DDC-B33A-B25D27D1D6DE}">
   <dimension ref="A1:F78"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="6" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="6" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -3961,496 +3961,496 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="6" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="B4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C6" s="6" t="s">
+    <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C7" s="6" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C13" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C20" s="6" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C20" s="6" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="6" t="s">
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C22" s="6" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C22" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C28" s="6" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C29" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C32" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C32" s="6" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="6" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C34" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="6" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C37" s="6" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B39" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C41" s="6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C41" s="6" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="6" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C44" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A43" s="2" t="s">
+    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C45" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C44" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C45" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C47" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B48" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C48" s="6" t="s">
+    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B49" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B49" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C49" s="6" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C50" s="6" t="s">
+    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B51" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B51" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C51" s="6" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="6" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C52" s="6" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="B53" s="3"/>
       <c r="C53" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C54" s="6" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C54" s="6" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C57" s="6" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C58" s="6" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="6" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="8" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A65" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65" s="6" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A66" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A67" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C67" s="6" t="s">
+    <row r="68" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="A68" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68" s="6" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A69" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69" s="6" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A72" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C72" s="6" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A73" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" s="6" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A74" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C74" s="6" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A77" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C77" s="6" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A78" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>374</v>
       </c>
     </row>
   </sheetData>
